--- a/sample-import-template.xlsx
+++ b/sample-import-template.xlsx
@@ -3,12 +3,12 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30606"/>
   <workbookPr/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{99946499-028E-4844-97FD-14519EDFFC61}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{13AF69CB-DABB-4EEF-B274-819948FACEAC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="0" windowHeight="0" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Samples Import" sheetId="1" r:id="rId1"/>
+    <sheet name="Samples" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191028"/>
   <extLst>
@@ -31,66 +31,510 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="20">
-  <si>
-    <t>Nom</t>
-  </si>
-  <si>
-    <t>Description</t>
-  </si>
-  <si>
-    <t>Statut</t>
-  </si>
-  <si>
-    <t>Categorie</t>
-  </si>
-  <si>
-    <t>Quantite</t>
-  </si>
-  <si>
-    <t>Stock</t>
-  </si>
-  <si>
-    <t>Poids</t>
-  </si>
-  <si>
-    <t>Ratio</t>
-  </si>
-  <si>
-    <t>Prix</t>
-  </si>
-  <si>
-    <t>Actif</t>
-  </si>
-  <si>
-    <t>Date fabrication</t>
-  </si>
-  <si>
-    <t>Heure fabrication</t>
-  </si>
-  <si>
-    <t>Commentaires</t>
-  </si>
-  <si>
-    <t>SAMPLE_IMPORT_001</t>
-  </si>
-  <si>
-    <t>Produit import exemple</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="309" uniqueCount="168">
+  <si>
+    <t>name</t>
+  </si>
+  <si>
+    <t>description</t>
+  </si>
+  <si>
+    <t>status</t>
+  </si>
+  <si>
+    <t>quantity</t>
+  </si>
+  <si>
+    <t>price</t>
+  </si>
+  <si>
+    <t>active</t>
+  </si>
+  <si>
+    <t>category</t>
+  </si>
+  <si>
+    <t>stock</t>
+  </si>
+  <si>
+    <t>comment</t>
+  </si>
+  <si>
+    <t>Sample-001</t>
+  </si>
+  <si>
+    <t>Sample de démonstration 1</t>
   </si>
   <si>
     <t>CREATED</t>
   </si>
   <si>
+    <t>true</t>
+  </si>
+  <si>
     <t>A</t>
   </si>
   <si>
-    <t>2025-01-01</t>
-  </si>
-  <si>
-    <t>08:30:00</t>
-  </si>
-  <si>
-    <t>Commentaire exemple</t>
+    <t>Commentaire 1</t>
+  </si>
+  <si>
+    <t>Sample-002</t>
+  </si>
+  <si>
+    <t>Sample de démonstration 2</t>
+  </si>
+  <si>
+    <t>ACTIVE</t>
+  </si>
+  <si>
+    <t>B</t>
+  </si>
+  <si>
+    <t>Commentaire 2</t>
+  </si>
+  <si>
+    <t>Sample-003</t>
+  </si>
+  <si>
+    <t>Sample de démonstration 3</t>
+  </si>
+  <si>
+    <t>ARCHIVED</t>
+  </si>
+  <si>
+    <t>C</t>
+  </si>
+  <si>
+    <t>Commentaire 3</t>
+  </si>
+  <si>
+    <t>Sample-004</t>
+  </si>
+  <si>
+    <t>Sample de démonstration 4</t>
+  </si>
+  <si>
+    <t>false</t>
+  </si>
+  <si>
+    <t>D</t>
+  </si>
+  <si>
+    <t>Commentaire 4</t>
+  </si>
+  <si>
+    <t>Sample-005</t>
+  </si>
+  <si>
+    <t>Sample de démonstration 5</t>
+  </si>
+  <si>
+    <t>Commentaire 5</t>
+  </si>
+  <si>
+    <t>Sample-006</t>
+  </si>
+  <si>
+    <t>Sample de démonstration 6</t>
+  </si>
+  <si>
+    <t>Commentaire 6</t>
+  </si>
+  <si>
+    <t>Sample-007</t>
+  </si>
+  <si>
+    <t>Sample de démonstration 7</t>
+  </si>
+  <si>
+    <t>Commentaire 7</t>
+  </si>
+  <si>
+    <t>Sample-008</t>
+  </si>
+  <si>
+    <t>Sample de démonstration 8</t>
+  </si>
+  <si>
+    <t>Commentaire 8</t>
+  </si>
+  <si>
+    <t>Sample-009</t>
+  </si>
+  <si>
+    <t>Sample de démonstration 9</t>
+  </si>
+  <si>
+    <t>Commentaire 9</t>
+  </si>
+  <si>
+    <t>Sample-010</t>
+  </si>
+  <si>
+    <t>Sample de démonstration 10</t>
+  </si>
+  <si>
+    <t>Commentaire 10</t>
+  </si>
+  <si>
+    <t>Sample-011</t>
+  </si>
+  <si>
+    <t>Sample de démonstration 11</t>
+  </si>
+  <si>
+    <t>Commentaire 11</t>
+  </si>
+  <si>
+    <t>Sample-012</t>
+  </si>
+  <si>
+    <t>Sample de démonstration 12</t>
+  </si>
+  <si>
+    <t>Commentaire 12</t>
+  </si>
+  <si>
+    <t>Sample-013</t>
+  </si>
+  <si>
+    <t>Sample de démonstration 13</t>
+  </si>
+  <si>
+    <t>Commentaire 13</t>
+  </si>
+  <si>
+    <t>Sample-014</t>
+  </si>
+  <si>
+    <t>Sample de démonstration 14</t>
+  </si>
+  <si>
+    <t>Commentaire 14</t>
+  </si>
+  <si>
+    <t>Sample-015</t>
+  </si>
+  <si>
+    <t>Sample de démonstration 15</t>
+  </si>
+  <si>
+    <t>Commentaire 15</t>
+  </si>
+  <si>
+    <t>Sample-016</t>
+  </si>
+  <si>
+    <t>Sample de démonstration 16</t>
+  </si>
+  <si>
+    <t>Commentaire 16</t>
+  </si>
+  <si>
+    <t>Sample-017</t>
+  </si>
+  <si>
+    <t>Sample de démonstration 17</t>
+  </si>
+  <si>
+    <t>Commentaire 17</t>
+  </si>
+  <si>
+    <t>Sample-018</t>
+  </si>
+  <si>
+    <t>Sample de démonstration 18</t>
+  </si>
+  <si>
+    <t>Commentaire 18</t>
+  </si>
+  <si>
+    <t>Sample-019</t>
+  </si>
+  <si>
+    <t>Sample de démonstration 19</t>
+  </si>
+  <si>
+    <t>Commentaire 19</t>
+  </si>
+  <si>
+    <t>Sample-020</t>
+  </si>
+  <si>
+    <t>Sample de démonstration 20</t>
+  </si>
+  <si>
+    <t>Commentaire 20</t>
+  </si>
+  <si>
+    <t>Sample-021</t>
+  </si>
+  <si>
+    <t>Sample de démonstration 21</t>
+  </si>
+  <si>
+    <t>Commentaire 21</t>
+  </si>
+  <si>
+    <t>Sample-022</t>
+  </si>
+  <si>
+    <t>Sample de démonstration 22</t>
+  </si>
+  <si>
+    <t>Commentaire 22</t>
+  </si>
+  <si>
+    <t>Sample-023</t>
+  </si>
+  <si>
+    <t>Sample de démonstration 23</t>
+  </si>
+  <si>
+    <t>Commentaire 23</t>
+  </si>
+  <si>
+    <t>Sample-024</t>
+  </si>
+  <si>
+    <t>Sample de démonstration 24</t>
+  </si>
+  <si>
+    <t>Commentaire 24</t>
+  </si>
+  <si>
+    <t>Sample-025</t>
+  </si>
+  <si>
+    <t>Sample de démonstration 25</t>
+  </si>
+  <si>
+    <t>Commentaire 25</t>
+  </si>
+  <si>
+    <t>Sample-026</t>
+  </si>
+  <si>
+    <t>Sample de démonstration 26</t>
+  </si>
+  <si>
+    <t>Commentaire 26</t>
+  </si>
+  <si>
+    <t>Sample-027</t>
+  </si>
+  <si>
+    <t>Sample de démonstration 27</t>
+  </si>
+  <si>
+    <t>Commentaire 27</t>
+  </si>
+  <si>
+    <t>Sample-028</t>
+  </si>
+  <si>
+    <t>Sample de démonstration 28</t>
+  </si>
+  <si>
+    <t>Commentaire 28</t>
+  </si>
+  <si>
+    <t>Sample-029</t>
+  </si>
+  <si>
+    <t>Sample de démonstration 29</t>
+  </si>
+  <si>
+    <t>Commentaire 29</t>
+  </si>
+  <si>
+    <t>Sample-030</t>
+  </si>
+  <si>
+    <t>Sample de démonstration 30</t>
+  </si>
+  <si>
+    <t>Commentaire 30</t>
+  </si>
+  <si>
+    <t>Sample-031</t>
+  </si>
+  <si>
+    <t>Sample de démonstration 31</t>
+  </si>
+  <si>
+    <t>Commentaire 31</t>
+  </si>
+  <si>
+    <t>Sample-032</t>
+  </si>
+  <si>
+    <t>Sample de démonstration 32</t>
+  </si>
+  <si>
+    <t>Commentaire 32</t>
+  </si>
+  <si>
+    <t>Sample-033</t>
+  </si>
+  <si>
+    <t>Sample de démonstration 33</t>
+  </si>
+  <si>
+    <t>Commentaire 33</t>
+  </si>
+  <si>
+    <t>Sample-034</t>
+  </si>
+  <si>
+    <t>Sample de démonstration 34</t>
+  </si>
+  <si>
+    <t>Commentaire 34</t>
+  </si>
+  <si>
+    <t>Sample-035</t>
+  </si>
+  <si>
+    <t>Sample de démonstration 35</t>
+  </si>
+  <si>
+    <t>Commentaire 35</t>
+  </si>
+  <si>
+    <t>Sample-036</t>
+  </si>
+  <si>
+    <t>Sample de démonstration 36</t>
+  </si>
+  <si>
+    <t>Commentaire 36</t>
+  </si>
+  <si>
+    <t>Sample-037</t>
+  </si>
+  <si>
+    <t>Sample de démonstration 37</t>
+  </si>
+  <si>
+    <t>Commentaire 37</t>
+  </si>
+  <si>
+    <t>Sample-038</t>
+  </si>
+  <si>
+    <t>Sample de démonstration 38</t>
+  </si>
+  <si>
+    <t>Commentaire 38</t>
+  </si>
+  <si>
+    <t>Sample-039</t>
+  </si>
+  <si>
+    <t>Sample de démonstration 39</t>
+  </si>
+  <si>
+    <t>Commentaire 39</t>
+  </si>
+  <si>
+    <t>Sample-040</t>
+  </si>
+  <si>
+    <t>Sample de démonstration 40</t>
+  </si>
+  <si>
+    <t>Commentaire 40</t>
+  </si>
+  <si>
+    <t>Sample-041</t>
+  </si>
+  <si>
+    <t>Sample de démonstration 41</t>
+  </si>
+  <si>
+    <t>Commentaire 41</t>
+  </si>
+  <si>
+    <t>Sample-042</t>
+  </si>
+  <si>
+    <t>Sample de démonstration 42</t>
+  </si>
+  <si>
+    <t>Commentaire 42</t>
+  </si>
+  <si>
+    <t>Sample-043</t>
+  </si>
+  <si>
+    <t>Sample de démonstration 43</t>
+  </si>
+  <si>
+    <t>Commentaire 43</t>
+  </si>
+  <si>
+    <t>Sample-044</t>
+  </si>
+  <si>
+    <t>Sample de démonstration 44</t>
+  </si>
+  <si>
+    <t>Commentaire 44</t>
+  </si>
+  <si>
+    <t>Sample-045</t>
+  </si>
+  <si>
+    <t>Sample de démonstration 45</t>
+  </si>
+  <si>
+    <t>Commentaire 45</t>
+  </si>
+  <si>
+    <t>Sample-046</t>
+  </si>
+  <si>
+    <t>Sample de démonstration 46</t>
+  </si>
+  <si>
+    <t>Commentaire 46</t>
+  </si>
+  <si>
+    <t>Sample-047</t>
+  </si>
+  <si>
+    <t>Sample de démonstration 47</t>
+  </si>
+  <si>
+    <t>Commentaire 47</t>
+  </si>
+  <si>
+    <t>Sample-048</t>
+  </si>
+  <si>
+    <t>Sample de démonstration 48</t>
+  </si>
+  <si>
+    <t>Commentaire 48</t>
+  </si>
+  <si>
+    <t>Sample-049</t>
+  </si>
+  <si>
+    <t>Sample de démonstration 49</t>
+  </si>
+  <si>
+    <t>Commentaire 49</t>
+  </si>
+  <si>
+    <t>Sample-050</t>
+  </si>
+  <si>
+    <t>Sample de démonstration 50</t>
+  </si>
+  <si>
+    <t>Commentaire 50</t>
   </si>
 </sst>
 </file>
@@ -108,21 +552,15 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
       <name val="Calibri"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1F4E78"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -139,7 +577,7 @@
   </cellStyleXfs>
   <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -155,6 +593,24 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="SamplesTable" displayName="SamplesTable" ref="A1:I51">
+  <autoFilter ref="A1:I51" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
+  <tableColumns count="9">
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="name"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="description"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="status"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="quantity"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="price"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="active"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="category"/>
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="stock"/>
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="comment"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -442,18 +898,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M2"/>
+  <dimension ref="A1:I51"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="30" customWidth="1"/>
-    <col min="2" max="2" width="40" customWidth="1"/>
-    <col min="3" max="3" width="18" customWidth="1"/>
-    <col min="4" max="10" width="12" customWidth="1"/>
-    <col min="11" max="12" width="18" customWidth="1"/>
-    <col min="13" max="13" width="40" customWidth="1"/>
+    <col min="1" max="9" width="22" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13">
+    <row r="1" spans="1:9">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -481,66 +932,1461 @@
       <c r="I1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="1" t="s">
+    </row>
+    <row r="2" spans="1:9">
+      <c r="A2" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="B2" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="C2" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="1" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13">
-      <c r="A2" t="s">
+      <c r="D2">
+        <v>5</v>
+      </c>
+      <c r="E2">
+        <v>11.49</v>
+      </c>
+      <c r="F2" t="s">
+        <v>12</v>
+      </c>
+      <c r="G2" t="s">
         <v>13</v>
       </c>
-      <c r="B2" t="s">
+      <c r="H2">
+        <v>10</v>
+      </c>
+      <c r="I2" t="s">
         <v>14</v>
       </c>
-      <c r="C2" t="s">
+    </row>
+    <row r="3" spans="1:9">
+      <c r="A3" t="s">
         <v>15</v>
       </c>
-      <c r="D2" t="s">
+      <c r="B3" t="s">
         <v>16</v>
       </c>
-      <c r="E2">
+      <c r="C3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D3">
+        <v>10</v>
+      </c>
+      <c r="E3">
+        <v>12.99</v>
+      </c>
+      <c r="F3" t="s">
+        <v>12</v>
+      </c>
+      <c r="G3" t="s">
+        <v>18</v>
+      </c>
+      <c r="H3">
+        <v>20</v>
+      </c>
+      <c r="I3" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9">
+      <c r="A4" t="s">
+        <v>20</v>
+      </c>
+      <c r="B4" t="s">
+        <v>21</v>
+      </c>
+      <c r="C4" t="s">
+        <v>22</v>
+      </c>
+      <c r="D4">
+        <v>15</v>
+      </c>
+      <c r="E4">
+        <v>14.49</v>
+      </c>
+      <c r="F4" t="s">
+        <v>12</v>
+      </c>
+      <c r="G4" t="s">
+        <v>23</v>
+      </c>
+      <c r="H4">
+        <v>30</v>
+      </c>
+      <c r="I4" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9">
+      <c r="A5" t="s">
+        <v>25</v>
+      </c>
+      <c r="B5" t="s">
+        <v>26</v>
+      </c>
+      <c r="C5" t="s">
+        <v>11</v>
+      </c>
+      <c r="D5">
+        <v>20</v>
+      </c>
+      <c r="E5">
+        <v>15.99</v>
+      </c>
+      <c r="F5" t="s">
+        <v>27</v>
+      </c>
+      <c r="G5" t="s">
+        <v>28</v>
+      </c>
+      <c r="H5">
+        <v>40</v>
+      </c>
+      <c r="I5" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9">
+      <c r="A6" t="s">
+        <v>30</v>
+      </c>
+      <c r="B6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C6" t="s">
+        <v>17</v>
+      </c>
+      <c r="D6">
+        <v>25</v>
+      </c>
+      <c r="E6">
+        <v>17.489999999999998</v>
+      </c>
+      <c r="F6" t="s">
+        <v>12</v>
+      </c>
+      <c r="G6" t="s">
+        <v>13</v>
+      </c>
+      <c r="H6">
+        <v>50</v>
+      </c>
+      <c r="I6" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9">
+      <c r="A7" t="s">
+        <v>33</v>
+      </c>
+      <c r="B7" t="s">
+        <v>34</v>
+      </c>
+      <c r="C7" t="s">
+        <v>22</v>
+      </c>
+      <c r="D7">
+        <v>30</v>
+      </c>
+      <c r="E7">
+        <v>18.989999999999998</v>
+      </c>
+      <c r="F7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G7" t="s">
+        <v>18</v>
+      </c>
+      <c r="H7">
+        <v>60</v>
+      </c>
+      <c r="I7" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9">
+      <c r="A8" t="s">
+        <v>36</v>
+      </c>
+      <c r="B8" t="s">
+        <v>37</v>
+      </c>
+      <c r="C8" t="s">
+        <v>11</v>
+      </c>
+      <c r="D8">
+        <v>35</v>
+      </c>
+      <c r="E8">
+        <v>20.49</v>
+      </c>
+      <c r="F8" t="s">
+        <v>12</v>
+      </c>
+      <c r="G8" t="s">
+        <v>23</v>
+      </c>
+      <c r="H8">
+        <v>70</v>
+      </c>
+      <c r="I8" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9">
+      <c r="A9" t="s">
+        <v>39</v>
+      </c>
+      <c r="B9" t="s">
+        <v>40</v>
+      </c>
+      <c r="C9" t="s">
+        <v>17</v>
+      </c>
+      <c r="D9">
+        <v>40</v>
+      </c>
+      <c r="E9">
+        <v>21.99</v>
+      </c>
+      <c r="F9" t="s">
+        <v>27</v>
+      </c>
+      <c r="G9" t="s">
+        <v>28</v>
+      </c>
+      <c r="H9">
+        <v>80</v>
+      </c>
+      <c r="I9" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9">
+      <c r="A10" t="s">
+        <v>42</v>
+      </c>
+      <c r="B10" t="s">
+        <v>43</v>
+      </c>
+      <c r="C10" t="s">
+        <v>22</v>
+      </c>
+      <c r="D10">
+        <v>45</v>
+      </c>
+      <c r="E10">
+        <v>23.49</v>
+      </c>
+      <c r="F10" t="s">
+        <v>12</v>
+      </c>
+      <c r="G10" t="s">
+        <v>13</v>
+      </c>
+      <c r="H10">
+        <v>90</v>
+      </c>
+      <c r="I10" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9">
+      <c r="A11" t="s">
+        <v>45</v>
+      </c>
+      <c r="B11" t="s">
+        <v>46</v>
+      </c>
+      <c r="C11" t="s">
+        <v>11</v>
+      </c>
+      <c r="D11">
+        <v>50</v>
+      </c>
+      <c r="E11">
+        <v>24.99</v>
+      </c>
+      <c r="F11" t="s">
+        <v>12</v>
+      </c>
+      <c r="G11" t="s">
+        <v>18</v>
+      </c>
+      <c r="H11">
         <v>100</v>
       </c>
-      <c r="F2">
+      <c r="I11" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9">
+      <c r="A12" t="s">
+        <v>48</v>
+      </c>
+      <c r="B12" t="s">
+        <v>49</v>
+      </c>
+      <c r="C12" t="s">
+        <v>17</v>
+      </c>
+      <c r="D12">
+        <v>55</v>
+      </c>
+      <c r="E12">
+        <v>26.49</v>
+      </c>
+      <c r="F12" t="s">
+        <v>12</v>
+      </c>
+      <c r="G12" t="s">
+        <v>23</v>
+      </c>
+      <c r="H12">
+        <v>110</v>
+      </c>
+      <c r="I12" t="s">
         <v>50</v>
       </c>
-      <c r="G2">
-        <v>12.5</v>
-      </c>
-      <c r="H2">
-        <v>0.8</v>
-      </c>
-      <c r="I2">
-        <v>99.99</v>
-      </c>
-      <c r="J2" t="b">
-        <v>1</v>
-      </c>
-      <c r="K2" t="s">
+    </row>
+    <row r="13" spans="1:9">
+      <c r="A13" t="s">
+        <v>51</v>
+      </c>
+      <c r="B13" t="s">
+        <v>52</v>
+      </c>
+      <c r="C13" t="s">
+        <v>22</v>
+      </c>
+      <c r="D13">
+        <v>60</v>
+      </c>
+      <c r="E13">
+        <v>27.99</v>
+      </c>
+      <c r="F13" t="s">
+        <v>27</v>
+      </c>
+      <c r="G13" t="s">
+        <v>28</v>
+      </c>
+      <c r="H13">
+        <v>120</v>
+      </c>
+      <c r="I13" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9">
+      <c r="A14" t="s">
+        <v>54</v>
+      </c>
+      <c r="B14" t="s">
+        <v>55</v>
+      </c>
+      <c r="C14" t="s">
+        <v>11</v>
+      </c>
+      <c r="D14">
+        <v>65</v>
+      </c>
+      <c r="E14">
+        <v>29.49</v>
+      </c>
+      <c r="F14" t="s">
+        <v>12</v>
+      </c>
+      <c r="G14" t="s">
+        <v>13</v>
+      </c>
+      <c r="H14">
+        <v>130</v>
+      </c>
+      <c r="I14" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9">
+      <c r="A15" t="s">
+        <v>57</v>
+      </c>
+      <c r="B15" t="s">
+        <v>58</v>
+      </c>
+      <c r="C15" t="s">
         <v>17</v>
       </c>
-      <c r="L2" t="s">
+      <c r="D15">
+        <v>70</v>
+      </c>
+      <c r="E15">
+        <v>30.99</v>
+      </c>
+      <c r="F15" t="s">
+        <v>12</v>
+      </c>
+      <c r="G15" t="s">
         <v>18</v>
       </c>
-      <c r="M2" t="s">
-        <v>19</v>
+      <c r="H15">
+        <v>140</v>
+      </c>
+      <c r="I15" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9">
+      <c r="A16" t="s">
+        <v>60</v>
+      </c>
+      <c r="B16" t="s">
+        <v>61</v>
+      </c>
+      <c r="C16" t="s">
+        <v>22</v>
+      </c>
+      <c r="D16">
+        <v>75</v>
+      </c>
+      <c r="E16">
+        <v>32.49</v>
+      </c>
+      <c r="F16" t="s">
+        <v>12</v>
+      </c>
+      <c r="G16" t="s">
+        <v>23</v>
+      </c>
+      <c r="H16">
+        <v>150</v>
+      </c>
+      <c r="I16" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9">
+      <c r="A17" t="s">
+        <v>63</v>
+      </c>
+      <c r="B17" t="s">
+        <v>64</v>
+      </c>
+      <c r="C17" t="s">
+        <v>11</v>
+      </c>
+      <c r="D17">
+        <v>80</v>
+      </c>
+      <c r="E17">
+        <v>33.99</v>
+      </c>
+      <c r="F17" t="s">
+        <v>27</v>
+      </c>
+      <c r="G17" t="s">
+        <v>28</v>
+      </c>
+      <c r="H17">
+        <v>160</v>
+      </c>
+      <c r="I17" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9">
+      <c r="A18" t="s">
+        <v>66</v>
+      </c>
+      <c r="B18" t="s">
+        <v>67</v>
+      </c>
+      <c r="C18" t="s">
+        <v>17</v>
+      </c>
+      <c r="D18">
+        <v>85</v>
+      </c>
+      <c r="E18">
+        <v>35.49</v>
+      </c>
+      <c r="F18" t="s">
+        <v>12</v>
+      </c>
+      <c r="G18" t="s">
+        <v>13</v>
+      </c>
+      <c r="H18">
+        <v>170</v>
+      </c>
+      <c r="I18" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9">
+      <c r="A19" t="s">
+        <v>69</v>
+      </c>
+      <c r="B19" t="s">
+        <v>70</v>
+      </c>
+      <c r="C19" t="s">
+        <v>22</v>
+      </c>
+      <c r="D19">
+        <v>90</v>
+      </c>
+      <c r="E19">
+        <v>36.99</v>
+      </c>
+      <c r="F19" t="s">
+        <v>12</v>
+      </c>
+      <c r="G19" t="s">
+        <v>18</v>
+      </c>
+      <c r="H19">
+        <v>180</v>
+      </c>
+      <c r="I19" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9">
+      <c r="A20" t="s">
+        <v>72</v>
+      </c>
+      <c r="B20" t="s">
+        <v>73</v>
+      </c>
+      <c r="C20" t="s">
+        <v>11</v>
+      </c>
+      <c r="D20">
+        <v>95</v>
+      </c>
+      <c r="E20">
+        <v>38.49</v>
+      </c>
+      <c r="F20" t="s">
+        <v>12</v>
+      </c>
+      <c r="G20" t="s">
+        <v>23</v>
+      </c>
+      <c r="H20">
+        <v>190</v>
+      </c>
+      <c r="I20" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9">
+      <c r="A21" t="s">
+        <v>75</v>
+      </c>
+      <c r="B21" t="s">
+        <v>76</v>
+      </c>
+      <c r="C21" t="s">
+        <v>17</v>
+      </c>
+      <c r="D21">
+        <v>100</v>
+      </c>
+      <c r="E21">
+        <v>39.99</v>
+      </c>
+      <c r="F21" t="s">
+        <v>27</v>
+      </c>
+      <c r="G21" t="s">
+        <v>28</v>
+      </c>
+      <c r="H21">
+        <v>200</v>
+      </c>
+      <c r="I21" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9">
+      <c r="A22" t="s">
+        <v>78</v>
+      </c>
+      <c r="B22" t="s">
+        <v>79</v>
+      </c>
+      <c r="C22" t="s">
+        <v>22</v>
+      </c>
+      <c r="D22">
+        <v>105</v>
+      </c>
+      <c r="E22">
+        <v>41.49</v>
+      </c>
+      <c r="F22" t="s">
+        <v>12</v>
+      </c>
+      <c r="G22" t="s">
+        <v>13</v>
+      </c>
+      <c r="H22">
+        <v>210</v>
+      </c>
+      <c r="I22" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9">
+      <c r="A23" t="s">
+        <v>81</v>
+      </c>
+      <c r="B23" t="s">
+        <v>82</v>
+      </c>
+      <c r="C23" t="s">
+        <v>11</v>
+      </c>
+      <c r="D23">
+        <v>110</v>
+      </c>
+      <c r="E23">
+        <v>42.99</v>
+      </c>
+      <c r="F23" t="s">
+        <v>12</v>
+      </c>
+      <c r="G23" t="s">
+        <v>18</v>
+      </c>
+      <c r="H23">
+        <v>220</v>
+      </c>
+      <c r="I23" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9">
+      <c r="A24" t="s">
+        <v>84</v>
+      </c>
+      <c r="B24" t="s">
+        <v>85</v>
+      </c>
+      <c r="C24" t="s">
+        <v>17</v>
+      </c>
+      <c r="D24">
+        <v>115</v>
+      </c>
+      <c r="E24">
+        <v>44.49</v>
+      </c>
+      <c r="F24" t="s">
+        <v>12</v>
+      </c>
+      <c r="G24" t="s">
+        <v>23</v>
+      </c>
+      <c r="H24">
+        <v>230</v>
+      </c>
+      <c r="I24" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9">
+      <c r="A25" t="s">
+        <v>87</v>
+      </c>
+      <c r="B25" t="s">
+        <v>88</v>
+      </c>
+      <c r="C25" t="s">
+        <v>22</v>
+      </c>
+      <c r="D25">
+        <v>120</v>
+      </c>
+      <c r="E25">
+        <v>45.99</v>
+      </c>
+      <c r="F25" t="s">
+        <v>27</v>
+      </c>
+      <c r="G25" t="s">
+        <v>28</v>
+      </c>
+      <c r="H25">
+        <v>240</v>
+      </c>
+      <c r="I25" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9">
+      <c r="A26" t="s">
+        <v>90</v>
+      </c>
+      <c r="B26" t="s">
+        <v>91</v>
+      </c>
+      <c r="C26" t="s">
+        <v>11</v>
+      </c>
+      <c r="D26">
+        <v>125</v>
+      </c>
+      <c r="E26">
+        <v>47.49</v>
+      </c>
+      <c r="F26" t="s">
+        <v>12</v>
+      </c>
+      <c r="G26" t="s">
+        <v>13</v>
+      </c>
+      <c r="H26">
+        <v>250</v>
+      </c>
+      <c r="I26" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9">
+      <c r="A27" t="s">
+        <v>93</v>
+      </c>
+      <c r="B27" t="s">
+        <v>94</v>
+      </c>
+      <c r="C27" t="s">
+        <v>17</v>
+      </c>
+      <c r="D27">
+        <v>130</v>
+      </c>
+      <c r="E27">
+        <v>48.99</v>
+      </c>
+      <c r="F27" t="s">
+        <v>12</v>
+      </c>
+      <c r="G27" t="s">
+        <v>18</v>
+      </c>
+      <c r="H27">
+        <v>260</v>
+      </c>
+      <c r="I27" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9">
+      <c r="A28" t="s">
+        <v>96</v>
+      </c>
+      <c r="B28" t="s">
+        <v>97</v>
+      </c>
+      <c r="C28" t="s">
+        <v>22</v>
+      </c>
+      <c r="D28">
+        <v>135</v>
+      </c>
+      <c r="E28">
+        <v>50.49</v>
+      </c>
+      <c r="F28" t="s">
+        <v>12</v>
+      </c>
+      <c r="G28" t="s">
+        <v>23</v>
+      </c>
+      <c r="H28">
+        <v>270</v>
+      </c>
+      <c r="I28" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9">
+      <c r="A29" t="s">
+        <v>99</v>
+      </c>
+      <c r="B29" t="s">
+        <v>100</v>
+      </c>
+      <c r="C29" t="s">
+        <v>11</v>
+      </c>
+      <c r="D29">
+        <v>140</v>
+      </c>
+      <c r="E29">
+        <v>51.99</v>
+      </c>
+      <c r="F29" t="s">
+        <v>27</v>
+      </c>
+      <c r="G29" t="s">
+        <v>28</v>
+      </c>
+      <c r="H29">
+        <v>280</v>
+      </c>
+      <c r="I29" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9">
+      <c r="A30" t="s">
+        <v>102</v>
+      </c>
+      <c r="B30" t="s">
+        <v>103</v>
+      </c>
+      <c r="C30" t="s">
+        <v>17</v>
+      </c>
+      <c r="D30">
+        <v>145</v>
+      </c>
+      <c r="E30">
+        <v>53.49</v>
+      </c>
+      <c r="F30" t="s">
+        <v>12</v>
+      </c>
+      <c r="G30" t="s">
+        <v>13</v>
+      </c>
+      <c r="H30">
+        <v>290</v>
+      </c>
+      <c r="I30" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9">
+      <c r="A31" t="s">
+        <v>105</v>
+      </c>
+      <c r="B31" t="s">
+        <v>106</v>
+      </c>
+      <c r="C31" t="s">
+        <v>22</v>
+      </c>
+      <c r="D31">
+        <v>150</v>
+      </c>
+      <c r="E31">
+        <v>54.99</v>
+      </c>
+      <c r="F31" t="s">
+        <v>12</v>
+      </c>
+      <c r="G31" t="s">
+        <v>18</v>
+      </c>
+      <c r="H31">
+        <v>300</v>
+      </c>
+      <c r="I31" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="32" spans="1:9">
+      <c r="A32" t="s">
+        <v>108</v>
+      </c>
+      <c r="B32" t="s">
+        <v>109</v>
+      </c>
+      <c r="C32" t="s">
+        <v>11</v>
+      </c>
+      <c r="D32">
+        <v>155</v>
+      </c>
+      <c r="E32">
+        <v>56.49</v>
+      </c>
+      <c r="F32" t="s">
+        <v>12</v>
+      </c>
+      <c r="G32" t="s">
+        <v>23</v>
+      </c>
+      <c r="H32">
+        <v>310</v>
+      </c>
+      <c r="I32" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="33" spans="1:9">
+      <c r="A33" t="s">
+        <v>111</v>
+      </c>
+      <c r="B33" t="s">
+        <v>112</v>
+      </c>
+      <c r="C33" t="s">
+        <v>17</v>
+      </c>
+      <c r="D33">
+        <v>160</v>
+      </c>
+      <c r="E33">
+        <v>57.99</v>
+      </c>
+      <c r="F33" t="s">
+        <v>27</v>
+      </c>
+      <c r="G33" t="s">
+        <v>28</v>
+      </c>
+      <c r="H33">
+        <v>320</v>
+      </c>
+      <c r="I33" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="34" spans="1:9">
+      <c r="A34" t="s">
+        <v>114</v>
+      </c>
+      <c r="B34" t="s">
+        <v>115</v>
+      </c>
+      <c r="C34" t="s">
+        <v>22</v>
+      </c>
+      <c r="D34">
+        <v>165</v>
+      </c>
+      <c r="E34">
+        <v>59.49</v>
+      </c>
+      <c r="F34" t="s">
+        <v>12</v>
+      </c>
+      <c r="G34" t="s">
+        <v>13</v>
+      </c>
+      <c r="H34">
+        <v>330</v>
+      </c>
+      <c r="I34" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="35" spans="1:9">
+      <c r="A35" t="s">
+        <v>117</v>
+      </c>
+      <c r="B35" t="s">
+        <v>118</v>
+      </c>
+      <c r="C35" t="s">
+        <v>11</v>
+      </c>
+      <c r="D35">
+        <v>170</v>
+      </c>
+      <c r="E35">
+        <v>60.99</v>
+      </c>
+      <c r="F35" t="s">
+        <v>12</v>
+      </c>
+      <c r="G35" t="s">
+        <v>18</v>
+      </c>
+      <c r="H35">
+        <v>340</v>
+      </c>
+      <c r="I35" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="36" spans="1:9">
+      <c r="A36" t="s">
+        <v>120</v>
+      </c>
+      <c r="B36" t="s">
+        <v>121</v>
+      </c>
+      <c r="C36" t="s">
+        <v>17</v>
+      </c>
+      <c r="D36">
+        <v>175</v>
+      </c>
+      <c r="E36">
+        <v>62.49</v>
+      </c>
+      <c r="F36" t="s">
+        <v>12</v>
+      </c>
+      <c r="G36" t="s">
+        <v>23</v>
+      </c>
+      <c r="H36">
+        <v>350</v>
+      </c>
+      <c r="I36" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="37" spans="1:9">
+      <c r="A37" t="s">
+        <v>123</v>
+      </c>
+      <c r="B37" t="s">
+        <v>124</v>
+      </c>
+      <c r="C37" t="s">
+        <v>22</v>
+      </c>
+      <c r="D37">
+        <v>180</v>
+      </c>
+      <c r="E37">
+        <v>63.99</v>
+      </c>
+      <c r="F37" t="s">
+        <v>27</v>
+      </c>
+      <c r="G37" t="s">
+        <v>28</v>
+      </c>
+      <c r="H37">
+        <v>360</v>
+      </c>
+      <c r="I37" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="38" spans="1:9">
+      <c r="A38" t="s">
+        <v>126</v>
+      </c>
+      <c r="B38" t="s">
+        <v>127</v>
+      </c>
+      <c r="C38" t="s">
+        <v>11</v>
+      </c>
+      <c r="D38">
+        <v>185</v>
+      </c>
+      <c r="E38">
+        <v>65.489999999999995</v>
+      </c>
+      <c r="F38" t="s">
+        <v>12</v>
+      </c>
+      <c r="G38" t="s">
+        <v>13</v>
+      </c>
+      <c r="H38">
+        <v>370</v>
+      </c>
+      <c r="I38" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="39" spans="1:9">
+      <c r="A39" t="s">
+        <v>129</v>
+      </c>
+      <c r="B39" t="s">
+        <v>130</v>
+      </c>
+      <c r="C39" t="s">
+        <v>17</v>
+      </c>
+      <c r="D39">
+        <v>190</v>
+      </c>
+      <c r="E39">
+        <v>66.989999999999995</v>
+      </c>
+      <c r="F39" t="s">
+        <v>12</v>
+      </c>
+      <c r="G39" t="s">
+        <v>18</v>
+      </c>
+      <c r="H39">
+        <v>380</v>
+      </c>
+      <c r="I39" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="40" spans="1:9">
+      <c r="A40" t="s">
+        <v>132</v>
+      </c>
+      <c r="B40" t="s">
+        <v>133</v>
+      </c>
+      <c r="C40" t="s">
+        <v>22</v>
+      </c>
+      <c r="D40">
+        <v>195</v>
+      </c>
+      <c r="E40">
+        <v>68.489999999999995</v>
+      </c>
+      <c r="F40" t="s">
+        <v>12</v>
+      </c>
+      <c r="G40" t="s">
+        <v>23</v>
+      </c>
+      <c r="H40">
+        <v>390</v>
+      </c>
+      <c r="I40" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="41" spans="1:9">
+      <c r="A41" t="s">
+        <v>135</v>
+      </c>
+      <c r="B41" t="s">
+        <v>136</v>
+      </c>
+      <c r="C41" t="s">
+        <v>11</v>
+      </c>
+      <c r="D41">
+        <v>200</v>
+      </c>
+      <c r="E41">
+        <v>69.989999999999995</v>
+      </c>
+      <c r="F41" t="s">
+        <v>27</v>
+      </c>
+      <c r="G41" t="s">
+        <v>28</v>
+      </c>
+      <c r="H41">
+        <v>400</v>
+      </c>
+      <c r="I41" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="42" spans="1:9">
+      <c r="A42" t="s">
+        <v>138</v>
+      </c>
+      <c r="B42" t="s">
+        <v>139</v>
+      </c>
+      <c r="C42" t="s">
+        <v>17</v>
+      </c>
+      <c r="D42">
+        <v>205</v>
+      </c>
+      <c r="E42">
+        <v>71.489999999999995</v>
+      </c>
+      <c r="F42" t="s">
+        <v>12</v>
+      </c>
+      <c r="G42" t="s">
+        <v>13</v>
+      </c>
+      <c r="H42">
+        <v>410</v>
+      </c>
+      <c r="I42" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="43" spans="1:9">
+      <c r="A43" t="s">
+        <v>141</v>
+      </c>
+      <c r="B43" t="s">
+        <v>142</v>
+      </c>
+      <c r="C43" t="s">
+        <v>22</v>
+      </c>
+      <c r="D43">
+        <v>210</v>
+      </c>
+      <c r="E43">
+        <v>72.989999999999995</v>
+      </c>
+      <c r="F43" t="s">
+        <v>12</v>
+      </c>
+      <c r="G43" t="s">
+        <v>18</v>
+      </c>
+      <c r="H43">
+        <v>420</v>
+      </c>
+      <c r="I43" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="44" spans="1:9">
+      <c r="A44" t="s">
+        <v>144</v>
+      </c>
+      <c r="B44" t="s">
+        <v>145</v>
+      </c>
+      <c r="C44" t="s">
+        <v>11</v>
+      </c>
+      <c r="D44">
+        <v>215</v>
+      </c>
+      <c r="E44">
+        <v>74.489999999999995</v>
+      </c>
+      <c r="F44" t="s">
+        <v>12</v>
+      </c>
+      <c r="G44" t="s">
+        <v>23</v>
+      </c>
+      <c r="H44">
+        <v>430</v>
+      </c>
+      <c r="I44" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="45" spans="1:9">
+      <c r="A45" t="s">
+        <v>147</v>
+      </c>
+      <c r="B45" t="s">
+        <v>148</v>
+      </c>
+      <c r="C45" t="s">
+        <v>17</v>
+      </c>
+      <c r="D45">
+        <v>220</v>
+      </c>
+      <c r="E45">
+        <v>75.989999999999995</v>
+      </c>
+      <c r="F45" t="s">
+        <v>27</v>
+      </c>
+      <c r="G45" t="s">
+        <v>28</v>
+      </c>
+      <c r="H45">
+        <v>440</v>
+      </c>
+      <c r="I45" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="46" spans="1:9">
+      <c r="A46" t="s">
+        <v>150</v>
+      </c>
+      <c r="B46" t="s">
+        <v>151</v>
+      </c>
+      <c r="C46" t="s">
+        <v>22</v>
+      </c>
+      <c r="D46">
+        <v>225</v>
+      </c>
+      <c r="E46">
+        <v>77.489999999999995</v>
+      </c>
+      <c r="F46" t="s">
+        <v>12</v>
+      </c>
+      <c r="G46" t="s">
+        <v>13</v>
+      </c>
+      <c r="H46">
+        <v>450</v>
+      </c>
+      <c r="I46" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="47" spans="1:9">
+      <c r="A47" t="s">
+        <v>153</v>
+      </c>
+      <c r="B47" t="s">
+        <v>154</v>
+      </c>
+      <c r="C47" t="s">
+        <v>11</v>
+      </c>
+      <c r="D47">
+        <v>230</v>
+      </c>
+      <c r="E47">
+        <v>78.989999999999995</v>
+      </c>
+      <c r="F47" t="s">
+        <v>12</v>
+      </c>
+      <c r="G47" t="s">
+        <v>18</v>
+      </c>
+      <c r="H47">
+        <v>460</v>
+      </c>
+      <c r="I47" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="48" spans="1:9">
+      <c r="A48" t="s">
+        <v>156</v>
+      </c>
+      <c r="B48" t="s">
+        <v>157</v>
+      </c>
+      <c r="C48" t="s">
+        <v>17</v>
+      </c>
+      <c r="D48">
+        <v>235</v>
+      </c>
+      <c r="E48">
+        <v>80.489999999999995</v>
+      </c>
+      <c r="F48" t="s">
+        <v>12</v>
+      </c>
+      <c r="G48" t="s">
+        <v>23</v>
+      </c>
+      <c r="H48">
+        <v>470</v>
+      </c>
+      <c r="I48" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="49" spans="1:9">
+      <c r="A49" t="s">
+        <v>159</v>
+      </c>
+      <c r="B49" t="s">
+        <v>160</v>
+      </c>
+      <c r="C49" t="s">
+        <v>22</v>
+      </c>
+      <c r="D49">
+        <v>240</v>
+      </c>
+      <c r="E49">
+        <v>81.99</v>
+      </c>
+      <c r="F49" t="s">
+        <v>27</v>
+      </c>
+      <c r="G49" t="s">
+        <v>28</v>
+      </c>
+      <c r="H49">
+        <v>480</v>
+      </c>
+      <c r="I49" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="50" spans="1:9">
+      <c r="A50" t="s">
+        <v>162</v>
+      </c>
+      <c r="B50" t="s">
+        <v>163</v>
+      </c>
+      <c r="C50" t="s">
+        <v>11</v>
+      </c>
+      <c r="D50">
+        <v>245</v>
+      </c>
+      <c r="E50">
+        <v>83.49</v>
+      </c>
+      <c r="F50" t="s">
+        <v>12</v>
+      </c>
+      <c r="G50" t="s">
+        <v>13</v>
+      </c>
+      <c r="H50">
+        <v>490</v>
+      </c>
+      <c r="I50" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="51" spans="1:9">
+      <c r="A51" t="s">
+        <v>165</v>
+      </c>
+      <c r="B51" t="s">
+        <v>166</v>
+      </c>
+      <c r="C51" t="s">
+        <v>17</v>
+      </c>
+      <c r="D51">
+        <v>250</v>
+      </c>
+      <c r="E51">
+        <v>84.99</v>
+      </c>
+      <c r="F51" t="s">
+        <v>12</v>
+      </c>
+      <c r="G51" t="s">
+        <v>18</v>
+      </c>
+      <c r="H51">
+        <v>500</v>
+      </c>
+      <c r="I51" t="s">
+        <v>167</v>
       </c>
     </row>
   </sheetData>
-  <dataValidations count="1">
-    <dataValidation type="list" sqref="C2:C5000" xr:uid="{00000000-0002-0000-0000-000000000000}">
-      <formula1>"CREATED,ACTIVE,ARCHIVED,DELETED"</formula1>
-    </dataValidation>
-  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
 </worksheet>
 </file>